--- a/Configs/Datas/ZZZ.CharacterAttribute.xlsx
+++ b/Configs/Datas/ZZZ.CharacterAttribute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB34829-EE24-4B01-B963-D5F9B6AFB040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB92C1F0-D0D8-415F-A874-8864A00F36C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="627" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="627" activeTab="3" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Allen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hp_base</t>
   </si>
   <si>
@@ -354,6 +350,10 @@
   </si>
   <si>
     <t>Ellen_FlashFreeze,0,6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -768,49 +768,49 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>27</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>28</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>29</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>31</v>
-      </c>
-      <c r="R1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -821,49 +821,49 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -882,49 +882,49 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
       <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
       <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>41</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>42</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>43</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>45</v>
-      </c>
-      <c r="R4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -932,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F5">
         <v>12000</v>
@@ -982,10 +982,10 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
         <v>91</v>
-      </c>
-      <c r="E6" t="s">
-        <v>92</v>
       </c>
       <c r="F6">
         <v>12000</v>
@@ -1029,13 +1029,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s">
         <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
       </c>
       <c r="F7">
         <v>12000</v>
@@ -1108,22 +1108,22 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
         <v>33</v>
-      </c>
-      <c r="G1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1134,22 +1134,22 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1168,22 +1168,22 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>54</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>55</v>
-      </c>
-      <c r="I4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>120</v>
@@ -1292,40 +1292,40 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>63</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>64</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>65</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>66</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>67</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>68</v>
-      </c>
-      <c r="O1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1336,40 +1336,40 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -1377,40 +1377,40 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
         <v>73</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>74</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>75</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>76</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>77</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>78</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>79</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>80</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>81</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>82</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>83</v>
-      </c>
-      <c r="O3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -1544,7 +1544,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -1611,13 +1611,13 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
-      </c>
-      <c r="F1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
         <v>88</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>89</v>
-      </c>
-      <c r="F2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1653,13 +1653,13 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" t="s">
         <v>85</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>86</v>
-      </c>
-      <c r="F4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/ZZZ.CharacterAttribute.xlsx
+++ b/Configs/Datas/ZZZ.CharacterAttribute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB92C1F0-D0D8-415F-A874-8864A00F36C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81202E8A-22C1-48DD-B25E-7F4860E86832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="627" activeTab="3" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -354,6 +354,18 @@
   </si>
   <si>
     <t>Ellen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseResilience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础抗打断等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1591,16 +1603,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72483E5-14A8-4FA8-A15B-52739B7BA6E5}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1619,8 +1632,11 @@
       <c r="F1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1636,13 +1652,16 @@
       <c r="F2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1661,23 +1680,35 @@
       <c r="F4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>94</v>
       </c>
       <c r="F7" t="s">
         <v>93</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
